--- a/output/北塩原村_アンケートと見込量の整合.xlsx
+++ b/output/北塩原村_アンケートと見込量の整合.xlsx
@@ -1558,7 +1558,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>アンケート分析報告書のクロス集計について、施設入所の利用希望23.7％、共同生活援助13.2％、短期入所10.5％、冬季の外出困難34.2％、訪問系を知らない23.7％の5つを優先して集計いただきたい。本調査は無記名であり回答者本人は特定できないため、アンケート内のクロス（年齢・障がい種別・住まい・介護者の有無）までを報告書で示し、そこから先の個別の確認は当方が行政データ（支給決定者台帳、障害支援区分、認定調査の行動関連項目）で行う。分母の定義（無回答を含めるか）は10テーマすべてで揃えたい</t>
+          <t>アンケート分析報告書のクロス集計について、施設入所の利用希望23.7％、共同生活援助13.2％、短期入所10.5％、冬季の外出困難34.2％、訪問系を知らない23.7％の５つを優先して集計いただきたい。本調査は無記名であり回答者本人は特定できないため、アンケート内のクロス（年齢・障がい種別・住まい・介護者の有無）までを報告書で示し、そこから先の個別の確認は当方が行政データ（支給決定者台帳、障害支援区分、認定調査の行動関連項目）で行う。分母の定義（無回答を含めるか）は10テーマすべてで揃えたい</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
